--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123423466</v>
+        <v>123422908</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>95141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410865</v>
+        <v>410986</v>
       </c>
       <c r="R2" t="n">
-        <v>6239208</v>
+        <v>6239185</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123422908</v>
+        <v>123423466</v>
       </c>
       <c r="B3" t="n">
-        <v>95139</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,37 +803,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410986</v>
+        <v>410865</v>
       </c>
       <c r="R3" t="n">
-        <v>6239185</v>
+        <v>6239208</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
         <v>123423420</v>
       </c>
       <c r="B4" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>123423120</v>
       </c>
       <c r="B5" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123422908</v>
       </c>
       <c r="B2" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123423420</v>
+        <v>123423120</v>
       </c>
       <c r="B4" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410885</v>
+        <v>410942</v>
       </c>
       <c r="R4" t="n">
-        <v>6239202</v>
+        <v>6239178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123423120</v>
+        <v>123423420</v>
       </c>
       <c r="B5" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410942</v>
+        <v>410885</v>
       </c>
       <c r="R5" t="n">
-        <v>6239178</v>
+        <v>6239202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123423466</v>
+        <v>123423120</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>95167</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410865</v>
+        <v>410942</v>
       </c>
       <c r="R2" t="n">
-        <v>6239208</v>
+        <v>6239178</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123423420</v>
+        <v>123423466</v>
       </c>
       <c r="B3" t="n">
-        <v>95150</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,37 +803,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410885</v>
+        <v>410865</v>
       </c>
       <c r="R3" t="n">
-        <v>6239202</v>
+        <v>6239208</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,6 +883,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
         <v>123422908</v>
       </c>
       <c r="B4" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123423120</v>
+        <v>123423420</v>
       </c>
       <c r="B5" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410942</v>
+        <v>410885</v>
       </c>
       <c r="R5" t="n">
-        <v>6239178</v>
+        <v>6239202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123423120</v>
+        <v>123423466</v>
       </c>
       <c r="B2" t="n">
-        <v>95167</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410942</v>
+        <v>410865</v>
       </c>
       <c r="R2" t="n">
-        <v>6239178</v>
+        <v>6239208</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +770,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123423466</v>
+        <v>123423120</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>95173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,47 +818,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410865</v>
+        <v>410942</v>
       </c>
       <c r="R3" t="n">
-        <v>6239208</v>
+        <v>6239178</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123422908</v>
+        <v>123423420</v>
       </c>
       <c r="B4" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410986</v>
+        <v>410885</v>
       </c>
       <c r="R4" t="n">
-        <v>6239185</v>
+        <v>6239202</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123423420</v>
+        <v>123422908</v>
       </c>
       <c r="B5" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410885</v>
+        <v>410986</v>
       </c>
       <c r="R5" t="n">
-        <v>6239202</v>
+        <v>6239185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123423466</v>
+        <v>123423120</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>95175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410865</v>
+        <v>410942</v>
       </c>
       <c r="R2" t="n">
-        <v>6239208</v>
+        <v>6239178</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123423120</v>
+        <v>123422908</v>
       </c>
       <c r="B3" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410942</v>
+        <v>410986</v>
       </c>
       <c r="R3" t="n">
-        <v>6239178</v>
+        <v>6239185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123423420</v>
+        <v>123423466</v>
       </c>
       <c r="B4" t="n">
-        <v>95173</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,37 +915,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410885</v>
+        <v>410865</v>
       </c>
       <c r="R4" t="n">
-        <v>6239202</v>
+        <v>6239208</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,6 +995,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123422908</v>
+        <v>123423420</v>
       </c>
       <c r="B5" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410986</v>
+        <v>410885</v>
       </c>
       <c r="R5" t="n">
-        <v>6239185</v>
+        <v>6239202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123423120</v>
       </c>
       <c r="B2" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123422908</v>
       </c>
       <c r="B3" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>123423420</v>
       </c>
       <c r="B5" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123423120</v>
+        <v>123423466</v>
       </c>
       <c r="B2" t="n">
-        <v>95683</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410942</v>
+        <v>410865</v>
       </c>
       <c r="R2" t="n">
-        <v>6239178</v>
+        <v>6239208</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +770,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123422908</v>
+        <v>123423420</v>
       </c>
       <c r="B3" t="n">
         <v>95683</v>
@@ -827,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410986</v>
+        <v>410885</v>
       </c>
       <c r="R3" t="n">
-        <v>6239185</v>
+        <v>6239202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123423466</v>
+        <v>123422908</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>95683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,47 +930,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410865</v>
+        <v>410986</v>
       </c>
       <c r="R4" t="n">
-        <v>6239208</v>
+        <v>6239185</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123423420</v>
+        <v>123423120</v>
       </c>
       <c r="B5" t="n">
         <v>95683</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410885</v>
+        <v>410942</v>
       </c>
       <c r="R5" t="n">
-        <v>6239202</v>
+        <v>6239178</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123423466</v>
+        <v>123423120</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>95683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410865</v>
+        <v>410942</v>
       </c>
       <c r="R2" t="n">
-        <v>6239208</v>
+        <v>6239178</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1026,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123423120</v>
+        <v>123423466</v>
       </c>
       <c r="B5" t="n">
-        <v>95683</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,37 +1027,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410942</v>
+        <v>410865</v>
       </c>
       <c r="R5" t="n">
-        <v>6239178</v>
+        <v>6239208</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stor skogshönsfågel lyfte från talltopp. Sågs 30 m. Ej tjädertuppstorlek</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123423120</v>
+        <v>123422908</v>
       </c>
       <c r="B2" t="n">
         <v>95683</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410942</v>
+        <v>410986</v>
       </c>
       <c r="R2" t="n">
-        <v>6239178</v>
+        <v>6239185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123423420</v>
+        <v>123423120</v>
       </c>
       <c r="B3" t="n">
         <v>95683</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410885</v>
+        <v>410942</v>
       </c>
       <c r="R3" t="n">
-        <v>6239202</v>
+        <v>6239178</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123422908</v>
+        <v>123423420</v>
       </c>
       <c r="B4" t="n">
         <v>95683</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410986</v>
+        <v>410885</v>
       </c>
       <c r="R4" t="n">
-        <v>6239185</v>
+        <v>6239202</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>123422908</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,12 +785,7 @@
         <v>123423120</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,12 +892,7 @@
         <v>123423420</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,12 +999,7 @@
         <v>123423466</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,6 +1115,119 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123445748</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fäje myr norr, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>410955</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6239323</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4595-2025 artfynd.xlsx
+++ b/artfynd/A 4595-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123422908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123423120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123423420</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123423466</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,8 +1253,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445748</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>